--- a/resultados/Fiscalizacion_Web_DM_agujas-hipodermicas_24-08-2026.xlsx
+++ b/resultados/Fiscalizacion_Web_DM_agujas-hipodermicas_24-08-2026.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Búsquedas Marketplace" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hallazgos'!$A$1:$K$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hallazgos'!$A$1:$K$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -562,22 +562,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aguja Hipodérmica 32G 4mm caja 100 unidades</t>
+          <t>Aguja Desechable 18G x 1 1/2" x 1 unidad</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://www.falabella.com/falabella-cl/product/120050255/Aguja-Hipodermica-32G*-4MM-*-100-Unidades/120050256</t>
+          <t>https://www.farmaciasahumada.cl/aguja-desechable-18-g-x-1-1-2-pulgadas-x-1-unidad-4248.html</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>GENERICO Aguja Hipodérmica 32G* 4MM * 100 Unidades</t>
+          <t>Aguja Desechable 18 G x 1 1/2 pulgadas x 1 unidad</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Falabella.com (falabella-cl)</t>
+          <t>Farmacias Ahumada</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Vendida bajo marca genérica 'GENERICO' sin fabricante identificable; no figura en el listado ISP de agujas hipodérmicas. Precio no visible en el fetch (bloqueado parcialmente por el sitio); verificar directamente en la publicación.</t>
+          <t>La publicación no declara marca ni fabricante. Sin marca no hay forma de cruzar contra el listado ISP. Calibre 18G x 1 1/2 sí corresponde a la categoría. Requerir al oferente el N° de registro sanitario.</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr"/>
@@ -603,17 +603,17 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Aguja Desechable 18G x 1 1/2" unidad</t>
+          <t>Aguja Desechable 26G x 1/2" x 1 unidad</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>https://www.farmaciasahumada.cl/aguja-desechable-18-g-x-1-1-2-pulgadas-x-1-unidad-4248.html</t>
+          <t>https://www.farmaciasahumada.cl/aguja-desechable-26-g-x-1-2-pulgada-1-un.-4326.html</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Aguja Desechable 18 G X 1 1/2 Pulgadas x 1 Unidad</t>
+          <t>Aguja Desechable 26 G x 1/2 pulgada 1 un.</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Producto rotulado 'P.Aux Sin Marca', sin marca comercial identificable. No coincide con ninguna marca del listado ISP. Precio $1.045 CLP.</t>
+          <t>Sin marca declarada. Calibre 26G x 1/2 dentro de la categoría. Mismo oferente que el caso anterior: conviene revisar toda su línea de agujas.</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr"/>
@@ -644,22 +644,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Aguja Desechable 26G x 1/2" unidad</t>
+          <t>Aguja Hipodérmica Estéril caja 100 unidades (18G/21G/23G/27G)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.farmaciasahumada.cl/aguja-desechable-26-g-x-1-2-pulgada-1-un.-4326.html</t>
+          <t>https://vitalitachile.cl/producto/aguja-hipodermica-esteril-100-unidades/</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Aguja Desechable 26 G X 1/2 Pulgada 1 Un.</t>
+          <t>Aguja Hipodérmica Estéril 100 unidades</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Farmacias Ahumada</t>
+          <t>Vitalita Chile</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Sin marca comercial identificable ('P.Aux Sin Marca'). Publicación activa aunque el producto figura sin stock al momento de la revisión; se reporta porque la oferta sigue publicada. Precio $1.045 CLP.</t>
+          <t>Ficha verificada directamente: no declara marca ni fabricante en ninguna parte, solo descripción genérica. Ofrece 4 calibres, todos dentro de la categoría. Precio $4.900-$7.900. PRIORITARIO.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr"/>
@@ -685,22 +685,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Agujas Basaglar 32G x 4mm x 10 unidades</t>
+          <t>Aguja Hipodérmica 19G x 1 1/2 caja x 100</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://www.farmaciasahumada.cl/agujas-basaglar-32g-x-4-mm-x-10-und-93387.html</t>
+          <t>https://afchilespa.cl/producto/aguja-hipodermica-19g-x-1-1-2-caja-x-100/</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Agujas Basaglar 32G X 4 Mm X 10 Und</t>
+          <t>Aguja Hipodermica 19G X 1 1/2 Caja X 100</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Farmacias Ahumada</t>
+          <t>AF Chile SpA</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Marca mostrada 'Nedtfine' no coincide con 'NEDFLEX' del listado ISP de agujas hipodérmicas. IMPORTANTE: podrían ser agujas para pluma/lapicera de insulina (compatibles con el análogo Basaglar), categoría regulatoria distinta a las agujas hipodérmicas de jeringa. Verificar clasificación correcta antes de fiscalizar. Precio $99.999 CLP (10 unid).</t>
+          <t>Sin marca en el título. El sitio devolvió 403 al intentar abrir la ficha, así que no se pudo verificar por texto ni por imagen. Se registra la limitación: requiere revisión manual antes de concluir.</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr"/>
@@ -726,22 +726,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Agujas Hipodérmicas 32G x 4mm caja 100 unidades</t>
+          <t>Aguja Hipodérmica 19G x 1 caja 100 unidades</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://ultraestetica.cl/products/agujas-hipodermicas-32g-4mm-caja-100-unds</t>
+          <t>https://articulo.mercadolibre.cl/MLC-640009079-aguja-hipodermica-19g-x-1-caja-100-unid-_JM</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Agujas Hipodermicas 32g 4mm Caja * 100 Unds.</t>
+          <t>Aguja HiPodérmica 19g X 1 Caja 100 Unid.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Ultra Estética (Chile, RM)</t>
+          <t>Vendedor Mercado Libre Chile</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Producto sin marca comercial identificable, comercializado para mesoterapia/uso estético (aplicación de toxina botulínica). Verificar si corresponde a la misma categoría regulatoria que agujas hipodérmicas de uso clínico general. Precio $19.990 CLP.</t>
+          <t>Sin marca en el título. Mercado Libre bloquea el acceso directo (403), no verificable por imagen. Calibre dentro de la categoría.</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr"/>
@@ -767,22 +767,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Agujas Hipodérmicas 32G x 6mm caja 100 unidades</t>
+          <t>Agujas Hipodérmicas caja x 100 unidades 20G-27G</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://ultraestetica.cl/products/agujas-hipodermicas-32g-6mm-caja-100-unds</t>
+          <t>https://articulo.mercadolibre.cl/MLC-434636621-agujas-hipodermicas-caja-x-100-unidades-20g-27g-_JM</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Agujas Hipodermicas 32g 6mm Caja * 100 Unds.</t>
+          <t>Agujas Hipodermicas Caja X 100 Unidades 20g 27g</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Ultra Estética (Chile, RM)</t>
+          <t>Vendedor Mercado Libre Chile</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Sin marca comercial identificable, uso mesoterapia/estética. Mismo oferente que otro hallazgo de esta corrida (Ultra Estética). Precio $18.990 CLP.</t>
+          <t>Sin marca declarada. Acceso bloqueado (403). Calibres 20G a 27G dentro de la categoría.</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr"/>
@@ -818,12 +818,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Agujas Hipodermicas 30g 13mm Caja * 100 Unds.</t>
+          <t>Agujas Hipodérmicas 30G x 13mm caja 100 unds</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Ultra Estética (Chile, RM)</t>
+          <t>Ultra Estética</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Sin marca comercial identificable. Calibre 30G más cercano al uso clínico estándar que a mesoterapia fina; oferente reincidente (Ultra Estética, ya con 2 hallazgos previos en esta corrida). Precio $4.790 CLP.</t>
+          <t>Sin marca declarada. 13mm equivale a 1/2 pulgada y 30G x 1/2 sí figura en el listado (Muncare DM 402/15, Nipro DM 630/24), así que se mantiene en categoría. Ojo: el oferente es una tienda de estética y el resto de su catálogo es mesoterapia, fuera de esta categoría.</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr"/>
@@ -849,39 +849,47 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Agujas Hipodérmicas 30G x 4mm caja 100 unidades</t>
+          <t>Agujas Hipodérmicas Desechables 23G x 1" caja 100 - Cranberry</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://ultraestetica.cl/products/agujas-hipodermicas-30g-4mm-caja-100-unds</t>
+          <t>https://www.mpmedical.cl/producto/agujas-hipodermicas-desechables-23g-x-1-caja-de-100-unid/</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Agujas Hipodermicas 30g 4mm Caja * 100 Unds.</t>
+          <t>Agujas Hipodérmicas Desechables 23G x 1 caja de 100 unid</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Ultra Estética (Chile, RM)</t>
+          <t>Mpmedical</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>NO REGISTRADO</t>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>CRANBERRY</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>DM 522/21</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Sin marca comercial identificable, uso mesoterapia/estética. Oferente reincidente (Ultra Estética, 3er hallazgo de esta corrida en el mismo sitio). Precio $18.990 CLP.</t>
+          <t>CORRECCIÓN respecto del reporte anterior, que citaba DM 622/24: ese registro solo ampara 21G x 1 1/2. El calibre 23G x 1 sí está cubierto por DM 522/21 (y por DM 397/15). Titular Reutter S.A.</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr"/>
@@ -890,39 +898,47 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Agujas Hipodérmicas 32G x 4mm Mesoterapia caja 100 unidades</t>
+          <t>Aguja Hipodérmica 30G x 1/2 Muncare</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://medic-dent.cl/producto/agujas-hipodermicas-32g-x-4mm-mesoterapia-caja-de-100-unidades/</t>
+          <t>https://medcare.cl/products/aguja-hipodermica-30gx-1-2</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Agujas Hipodérmicas 32G x 4mm – Mesoterapia (Caja de 100 unidades)</t>
+          <t>Aguja Hipodérmica 30G x 1/2 Muncare</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Medic Dent</t>
+          <t>Medcare</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>NO REGISTRADO</t>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>MUNCARE</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>DM 402/15</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Sin marca comercial identificable. Descripción indica uso para administración de toxina botulínica (rejuvenecimiento facial). Verificar categoría regulatoria aplicable (mesoterapia vs. uso clínico general). Precio $36.000 CLP.</t>
+          <t>Calibre 30G 1/2 verificado en el registro. Titular Femsa Salud SpA.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr"/>
@@ -931,39 +947,47 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Agujas Hipodérmicas 32G x 6mm Mesoterapia caja 100 unidades</t>
+          <t>Aguja Hipodérmica caja x 100 unidades Muncare</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://medic-dent.cl/producto/agujas-hipodermicas-32g-x-6mm-mesoterapia-caja-de-100-unidades/</t>
+          <t>https://geerdink.cl/products/aguja-hipodermica-caja-x-100-unidades-muncare</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Agujas Hipodérmicas 32G x 6mm – Mesoterapia (Caja de 100 unidades)</t>
+          <t>Aguja Hipodérmica Caja x 100 unidades Muncare</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Medic Dent</t>
+          <t>Geerdink</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>NO REGISTRADO</t>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>MUNCARE</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>DM 402/15</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Sin marca comercial identificable, uso mesoterapia/estética. Mismo oferente que hallazgo anterior en esta corrida. Precio $36.000 CLP.</t>
+          <t>Ofrece 18G a 30G; los calibres publicados están dentro de los amparados. Precio $3.090.</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr"/>
@@ -972,22 +996,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Agujas Hipodérmicas Desechables 23G x 1" caja de 100 unid</t>
+          <t>Aguja Hipodérmica caja x 100 unidades Cranberry</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://www.mpmedical.cl/producto/agujas-hipodermicas-desechables-23g-x-1-caja-de-100-unid/</t>
+          <t>https://deltamed.cl/tienda/producto/aguja-hipodermica-caja-x-100-unidades-cranberry/</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Agujas Hipodérmicas Desechables 23G x 1″ caja de 100 unid</t>
+          <t>Aguja Hipodérmica caja x 100 unidades Cranberry</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Mpmedical</t>
+          <t>Deltamed</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1002,7 +1026,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>DM 622/24</t>
+          <t>DM 397/15</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -1012,7 +1036,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia por marca comercial (Cranberry) con registro vigente a nombre de Reutter S.A. Precio $2.190 CLP.</t>
+          <t>La publicación no especifica calibre. Se cita DM 397/15 por ser el de mayor cobertura de la marca (19G, 21G, 23G, 25G, 27G). Verificar calibre concreto si se fiscaliza.</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr"/>
@@ -1021,22 +1045,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Aguja Hipodérmica 30G x 1/2 Muncare</t>
+          <t>Agujas Hipodérmicas Cranberry caja 100 unidades</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>https://medcare.cl/products/aguja-hipodermica-30gx-1-2</t>
+          <t>https://klinetix.cl/products/agujas-hipodermicas-cranberry</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Aguja Hipodérmica 30gx 1/2</t>
+          <t>Agujas Hipodérmicas Cranberry</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Medcare</t>
+          <t>Klinetix</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1046,12 +1070,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>MUNCARE</t>
+          <t>CRANBERRY</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>DM 402/15</t>
+          <t>DM 397/15</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -1061,7 +1085,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Coincidencia por marca comercial (Muncare) con registro vigente a nombre de Femsa Salud SpA. Precio $100 CLP (verificar si corresponde a unidad o caja).</t>
+          <t>Calibre no especificado en la publicación. Klinetix además tiene marca propia registrada (DM 656/25).</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr"/>
@@ -1070,22 +1094,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Aguja Hipodérmica caja x 100 unidades Muncare</t>
+          <t>Aguja Hipodérmica 24G x 1" 100 unidades Nipro</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://geerdink.cl/products/aguja-hipodermica-caja-x-100-unidades-muncare</t>
+          <t>https://www.vicamat.cl/aguja-hipodermica-24g-x-1-100-und-nipro</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Aguja Hipodérmica Caja x 100 unidades Muncare</t>
+          <t>Aguja Hipodermica 24G x 1 100 Und - Nipro</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Geerdink</t>
+          <t>Vicamat</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1095,12 +1119,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>MUNCARE</t>
+          <t>NIPRO</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>DM 402/15</t>
+          <t>DM/10AG/0175/09</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -1110,7 +1134,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia por marca comercial (Muncare). Precio $3.090 CLP.</t>
+          <t>CORRECCIÓN respecto del reporte anterior, que citaba DM 630/24: ese registro no incluye 24G. El calibre 24G x 1 sí está en DM/10AG/0175/09. Solo dos registros del listado cubren 24G.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr"/>
@@ -1119,22 +1143,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Aguja Pentapoint 32G x 4 x 5 unidades BD Ultra-Fine</t>
+          <t>Caja Aguja Hipodérmica 27G x 1/2 - 100 unidades Nipro Flomax</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>https://www.farmaciasahumada.cl/aguja-pentapoint-32-g-x-4-x-5-unidades-86284.html</t>
+          <t>https://medcare.cl/products/caja-aguja-hipodermica-27g-x-1-2-100-unidades</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Aguja Pentapoint 32 G x 4 x 5 Unidades</t>
+          <t>Caja Aguja Hipodérmica 27G x 1/2 -100 Unidades</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Farmacias Ahumada</t>
+          <t>Medcare</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1144,12 +1168,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>BECTON DICKINSON</t>
+          <t>NIPRO</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>DM/10AG/0219/09</t>
+          <t>DM 630/24</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -1159,7 +1183,7 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Marca BD Ultra-Fine, coincide con Becton Dickinson del listado ISP. Precio $556 CLP/unidad ($2.779 el pack de 5).</t>
+          <t>El título es genérico pero la descripción declara Nipro Flomax. Calibre 27G x 1/2 verificado en DM 630/24. Precio $8.990.</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr"/>
@@ -1168,22 +1192,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Aguja Hipodérmica caja x 100 unidades Cranberry</t>
+          <t>Aguja Hipodérmica 19G x 1 1/2 Medicaltek caja 100 unidades</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://deltamed.cl/tienda/producto/aguja-hipodermica-caja-x-100-unidades-cranberry/</t>
+          <t>https://www.osm.cl/product-page/aguja-hipodermica-19g-x-1-1-2-medicaltek-caja-100-unidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Aguja Hipodérmica Caja X 100 Unidades Cranberry</t>
+          <t>Aguja Hipodermica 19G x 1 1/2 Medicaltek caja 100 unidades</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Deltamed</t>
+          <t>OSM Ltda</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1193,12 +1217,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>CRANBERRY</t>
+          <t>MEDICALTEK</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>DM 622/24</t>
+          <t>DM 412/15</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -1208,7 +1232,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia por marca comercial (Cranberry). Precio $2.490 CLP.</t>
+          <t>Calibre 19G x 1 1/2 verificado en el registro. Titular Medicaltek Chile S.A. Precio $4.740.</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr"/>
@@ -1217,22 +1241,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Aguja Hipodérmica Estéril caja 100 unid Cranberry</t>
+          <t>Agujas hipodérmicas Cranberry caja 100 unidades</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>https://klinetix.cl/products/agujas-hipodermicas-cranberry</t>
+          <t>https://nexodental.cl/product/agujas-hipodermicas-100-unidades-cranberry/</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Aguja Hipodérmica Estéril | Caja 100 uni | Cranberry</t>
+          <t>agujas hipodérmicas Cranberry | Caja 100 unidades</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Klinetix</t>
+          <t>Nexo Dental</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1247,7 +1271,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>DM 622/24</t>
+          <t>DM 397/15</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -1257,63 +1281,14 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Coincidencia por marca comercial (Cranberry). Precio $2.130 CLP.</t>
+          <t>Calibre no especificado. Oferente del rubro dental.</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Aguja Hipodérmica 24G x 1" 100 Und Nipro</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vicamat.cl/aguja-hipodermica-24g-x-1-100-und-nipro</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Aguja Hipodermica 24G x 1" 100 Und - Nipro</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Vicamat</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>NIPRO</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>DM 630/24</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Coincidencia por marca comercial (Nipro). Precio no visible en el fetch; verificar directamente en la publicación.</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K18"/>
+  <autoFilter ref="A1:K17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1324,7 +1299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1386,25 +1361,58 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>agujas hipodérmicas; aguja hipodermica</t>
+          <t>agujas hipodermicas</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Nipro, Cranberry, Deltamed (vendedor, producto marca Cranberry)</t>
+          <t>Nipro (registrada) y publicaciones sin marca declarada</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>~280 publicaciones (indicado por el sitio en búsquedas relacionadas)</t>
+          <t>no determinable, listado bloqueado</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Acceso directo a publicaciones individuales (articulo.mercadolibre.cl) bloqueado con HTTP 403 por robots.txt, comportamiento ya documentado para este marketplace. Las marcas detectadas en títulos de resultados de búsqueda (Nipro, Cranberry) SÍ figuran en el listado ISP. No se detectaron marcas ausentes del listado en los títulos visibles desde los resultados de búsqueda; se recomienda revisión manual periódica dado el alto volumen de publicaciones (~280) que no pudo auditarse publicación por publicación.</t>
+          <t>403 tanto en el listado como en las publicaciones individuales. Dos publicaciones sin marca quedaron en la hoja principal. Revisar manualmente filtrando por marca contra las 18 con registro vigente.</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>(no aplica) Descartados por categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>https://ultraestetica.cl/ | https://medic-dent.cl/ | https://www.falabella.com/falabella-cl/ | https://www.farmaciasahumada.cl/</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>agujas 32G 4mm / 6mm, mesoterapia, lapicera insulina</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>BD Ultra-Fine Pentapoint, Basaglar, sin marca</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>8 publicaciones</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>OCHO productos encontrados quedaron FUERA del reporte por no pertenecer a esta categoría: son agujas para lapicera de insulina y de mesoterapia (32G x 4mm, 32G x 6mm, 30G x 4mm), medidas en milímetros. El listado ISP de agujas hipodérmicas va de 16G a 30G en pulgadas y NO contiene ningún 32G. Se dejan documentados por si ANDIM quiere fiscalizarlos contra el listado que corresponda: Falabella 32G 4mm; Ahumada Agujas Basaglar 32G 4mm; Ahumada BD Pentapoint 32G x 4 (el reporte anterior lo dio por REGISTRADO citando DM/10AG/0219/09, que solo cubre 18G a 27G: era un falso positivo); Ultra Estética 32G 4mm, 32G 6mm y 30G 4mm; Medic Dent 32G 4mm y 32G 6mm.</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resultados/Fiscalizacion_Web_DM_agujas-hipodermicas_24-08-2026.xlsx
+++ b/resultados/Fiscalizacion_Web_DM_agujas-hipodermicas_24-08-2026.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Hallazgos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Búsquedas Marketplace" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Anexo — sobre el tope" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Búsquedas Marketplace" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hallazgos'!$A$1:$K$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hallazgos'!$A$1:$K$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +41,10 @@
     <font>
       <b val="1"/>
       <color rgb="001E6B1E"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="7">
@@ -101,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -121,6 +126,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -993,307 +999,230 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Aguja Hipodérmica caja x 100 unidades Cranberry</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>https://deltamed.cl/tienda/producto/aguja-hipodermica-caja-x-100-unidades-cranberry/</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Aguja Hipodérmica caja x 100 unidades Cranberry</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Deltamed</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>CRANBERRY</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>DM 397/15</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>La publicación no especifica calibre. Se cita DM 397/15 por ser el de mayor cobertura de la marca (19G, 21G, 23G, 25G, 27G). Verificar calibre concreto si se fiscaliza.</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Agujas Hipodérmicas Cranberry caja 100 unidades</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>https://klinetix.cl/products/agujas-hipodermicas-cranberry</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Agujas Hipodérmicas Cranberry</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Klinetix</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>CRANBERRY</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>DM 397/15</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>Calibre no especificado en la publicación. Klinetix además tiene marca propia registrada (DM 656/25).</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Aguja Hipodérmica 24G x 1" 100 unidades Nipro</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vicamat.cl/aguja-hipodermica-24g-x-1-100-und-nipro</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Aguja Hipodermica 24G x 1 100 Und - Nipro</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Vicamat</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>NIPRO</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>DM/10AG/0175/09</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>CORRECCIÓN respecto del reporte anterior, que citaba DM 630/24: ese registro no incluye 24G. El calibre 24G x 1 sí está en DM/10AG/0175/09. Solo dos registros del listado cubren 24G.</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Caja Aguja Hipodérmica 27G x 1/2 - 100 unidades Nipro Flomax</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>https://medcare.cl/products/caja-aguja-hipodermica-27g-x-1-2-100-unidades</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Caja Aguja Hipodérmica 27G x 1/2 -100 Unidades</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Medcare</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>NIPRO</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>DM 630/24</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>El título es genérico pero la descripción declara Nipro Flomax. Calibre 27G x 1/2 verificado en DM 630/24. Precio $8.990.</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Aguja Hipodérmica 19G x 1 1/2 Medicaltek caja 100 unidades</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.osm.cl/product-page/aguja-hipodermica-19g-x-1-1-2-medicaltek-caja-100-unidades</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Aguja Hipodermica 19G x 1 1/2 Medicaltek caja 100 unidades</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>OSM Ltda</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>MEDICALTEK</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>DM 412/15</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Calibre 19G x 1 1/2 verificado en el registro. Titular Medicaltek Chile S.A. Precio $4.740.</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Agujas hipodérmicas Cranberry caja 100 unidades</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>https://nexodental.cl/product/agujas-hipodermicas-100-unidades-cranberry/</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>agujas hipodérmicas Cranberry | Caja 100 unidades</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Nexo Dental</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>CRANBERRY</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>DM 397/15</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>Calibre no especificado. Oferente del rubro dental.</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K17"/>
+  <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Nombre de DM ofertado</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Oferente</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Clasificación</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Aguja Hipodérmica caja x 100 unidades Cranberry</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://deltamed.cl/tienda/producto/aguja-hipodermica-caja-x-100-unidades-cranberry/</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Deltamed</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>La publicación no especifica calibre. Se cita DM 397/15 por ser el de mayor cobertura de la marca (19G, 21G, 23G, 25G, 27G). Verificar calibre concreto si se fiscaliza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Agujas Hipodérmicas Cranberry caja 100 unidades</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>https://klinetix.cl/products/agujas-hipodermicas-cranberry</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Klinetix</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Calibre no especificado en la publicación. Klinetix además tiene marca propia registrada (DM 656/25).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Aguja Hipodérmica 24G x 1" 100 unidades Nipro</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vicamat.cl/aguja-hipodermica-24g-x-1-100-und-nipro</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Vicamat</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>CORRECCIÓN respecto del reporte anterior, que citaba DM 630/24: ese registro no incluye 24G. El calibre 24G x 1 sí está en DM/10AG/0175/09. Solo dos registros del listado cubren 24G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Caja Aguja Hipodérmica 27G x 1/2 - 100 unidades Nipro Flomax</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>https://medcare.cl/products/caja-aguja-hipodermica-27g-x-1-2-100-unidades</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Medcare</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>El título es genérico pero la descripción declara Nipro Flomax. Calibre 27G x 1/2 verificado en DM 630/24. Precio $8.990.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Aguja Hipodérmica 19G x 1 1/2 Medicaltek caja 100 unidades</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.osm.cl/product-page/aguja-hipodermica-19g-x-1-1-2-medicaltek-caja-100-unidades</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>OSM Ltda</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Calibre 19G x 1 1/2 verificado en el registro. Titular Medicaltek Chile S.A. Precio $4.740.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Agujas hipodérmicas Cranberry caja 100 unidades</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>https://nexodental.cl/product/agujas-hipodermicas-100-unidades-cranberry/</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Nexo Dental</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Calibre no especificado. Oferente del rubro dental.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Estas 6 ofertas se detectaron en la misma búsqueda pero quedaron fuera del reporte por el tope de 10 hallazgos. NO requieren revisión esta semana. Al no quedar registradas como evaluadas, vuelven a considerarse en la próxima corrida de la categoría.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/resultados/Fiscalizacion_Web_DM_agujas-hipodermicas_24-08-2026.xlsx
+++ b/resultados/Fiscalizacion_Web_DM_agujas-hipodermicas_24-08-2026.xlsx
@@ -8,11 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Hallazgos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Anexo — sobre el tope" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Búsquedas Marketplace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Búsquedas Marketplace" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hallazgos'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hallazgos'!$A$1:$K$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,10 +40,6 @@
     <font>
       <b val="1"/>
       <color rgb="001E6B1E"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="7">
@@ -106,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -126,7 +121,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -999,230 +993,307 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aguja Hipodérmica caja x 100 unidades Cranberry</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://deltamed.cl/tienda/producto/aguja-hipodermica-caja-x-100-unidades-cranberry/</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Aguja Hipodérmica caja x 100 unidades Cranberry</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Deltamed</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>CRANBERRY</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>DM 397/15</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>La publicación no especifica calibre. Se cita DM 397/15 por ser el de mayor cobertura de la marca (19G, 21G, 23G, 25G, 27G). Verificar calibre concreto si se fiscaliza.</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Agujas Hipodérmicas Cranberry caja 100 unidades</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>https://klinetix.cl/products/agujas-hipodermicas-cranberry</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Agujas Hipodérmicas Cranberry</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Klinetix</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>CRANBERRY</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>DM 397/15</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Calibre no especificado en la publicación. Klinetix además tiene marca propia registrada (DM 656/25).</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Aguja Hipodérmica 24G x 1" 100 unidades Nipro</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vicamat.cl/aguja-hipodermica-24g-x-1-100-und-nipro</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Aguja Hipodermica 24G x 1 100 Und - Nipro</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Vicamat</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>NIPRO</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>DM/10AG/0175/09</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>CORRECCIÓN respecto del reporte anterior, que citaba DM 630/24: ese registro no incluye 24G. El calibre 24G x 1 sí está en DM/10AG/0175/09. Solo dos registros del listado cubren 24G.</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Caja Aguja Hipodérmica 27G x 1/2 - 100 unidades Nipro Flomax</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>https://medcare.cl/products/caja-aguja-hipodermica-27g-x-1-2-100-unidades</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Caja Aguja Hipodérmica 27G x 1/2 -100 Unidades</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Medcare</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>NIPRO</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>DM 630/24</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>El título es genérico pero la descripción declara Nipro Flomax. Calibre 27G x 1/2 verificado en DM 630/24. Precio $8.990.</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Aguja Hipodérmica 19G x 1 1/2 Medicaltek caja 100 unidades</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.osm.cl/product-page/aguja-hipodermica-19g-x-1-1-2-medicaltek-caja-100-unidades</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Aguja Hipodermica 19G x 1 1/2 Medicaltek caja 100 unidades</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>OSM Ltda</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>MEDICALTEK</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>DM 412/15</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Calibre 19G x 1 1/2 verificado en el registro. Titular Medicaltek Chile S.A. Precio $4.740.</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Agujas hipodérmicas Cranberry caja 100 unidades</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>https://nexodental.cl/product/agujas-hipodermicas-100-unidades-cranberry/</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>agujas hipodérmicas Cranberry | Caja 100 unidades</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Nexo Dental</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>CRANBERRY</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>DM 397/15</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Calibre no especificado. Oferente del rubro dental.</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K11"/>
+  <autoFilter ref="A1:K17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Nombre de DM ofertado</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Oferente</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Clasificación</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Aguja Hipodérmica caja x 100 unidades Cranberry</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>https://deltamed.cl/tienda/producto/aguja-hipodermica-caja-x-100-unidades-cranberry/</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Deltamed</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>La publicación no especifica calibre. Se cita DM 397/15 por ser el de mayor cobertura de la marca (19G, 21G, 23G, 25G, 27G). Verificar calibre concreto si se fiscaliza.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Agujas Hipodérmicas Cranberry caja 100 unidades</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>https://klinetix.cl/products/agujas-hipodermicas-cranberry</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Klinetix</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Calibre no especificado en la publicación. Klinetix además tiene marca propia registrada (DM 656/25).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Aguja Hipodérmica 24G x 1" 100 unidades Nipro</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vicamat.cl/aguja-hipodermica-24g-x-1-100-und-nipro</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Vicamat</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>CORRECCIÓN respecto del reporte anterior, que citaba DM 630/24: ese registro no incluye 24G. El calibre 24G x 1 sí está en DM/10AG/0175/09. Solo dos registros del listado cubren 24G.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Caja Aguja Hipodérmica 27G x 1/2 - 100 unidades Nipro Flomax</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>https://medcare.cl/products/caja-aguja-hipodermica-27g-x-1-2-100-unidades</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Medcare</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>El título es genérico pero la descripción declara Nipro Flomax. Calibre 27G x 1/2 verificado en DM 630/24. Precio $8.990.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Aguja Hipodérmica 19G x 1 1/2 Medicaltek caja 100 unidades</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.osm.cl/product-page/aguja-hipodermica-19g-x-1-1-2-medicaltek-caja-100-unidades</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>OSM Ltda</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Calibre 19G x 1 1/2 verificado en el registro. Titular Medicaltek Chile S.A. Precio $4.740.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Agujas hipodérmicas Cranberry caja 100 unidades</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>https://nexodental.cl/product/agujas-hipodermicas-100-unidades-cranberry/</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Nexo Dental</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Calibre no especificado. Oferente del rubro dental.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Estas 6 ofertas se detectaron en la misma búsqueda pero quedaron fuera del reporte por el tope de 10 hallazgos. NO requieren revisión esta semana. Al no quedar registradas como evaluadas, vuelven a considerarse en la próxima corrida de la categoría.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
